--- a/outputs/top100_middle/Top100_FIDCs_Revisao_Middle.xlsx
+++ b/outputs/top100_middle/Top100_FIDCs_Revisao_Middle.xlsx
@@ -935,7 +935,11 @@
       <c r="S4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="T4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>C · Indústria de transformação</t>
+        </is>
+      </c>
       <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="inlineStr"/>
@@ -944,7 +948,11 @@
           <t>BRF*</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1162,12 +1170,20 @@
       <c r="S7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="T7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U7" s="5" t="inlineStr"/>
       <c r="V7" s="5" t="inlineStr"/>
       <c r="W7" s="5" t="inlineStr"/>
       <c r="X7" s="5" t="inlineStr"/>
-      <c r="Y7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1276,7 +1292,11 @@
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr"/>
-      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1364,7 +1384,11 @@
       <c r="S9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="T9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U9" s="5" t="inlineStr"/>
       <c r="V9" s="5" t="inlineStr"/>
       <c r="W9" s="5" t="inlineStr"/>
@@ -1457,12 +1481,20 @@
       <c r="S10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="T10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr"/>
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr"/>
-      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1855,7 +1887,11 @@
       <c r="S16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr"/>
       <c r="W16" s="2" t="inlineStr"/>
@@ -1907,21 +1943,49 @@
           <t>Multicarteira Outros</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>87.163.234/0001-38</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>SABEMI SEGURADORA SA</t>
+        </is>
+      </c>
       <c r="M17" s="5" t="inlineStr"/>
-      <c r="N17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>Sociedade seguradora de seguros vida</t>
+        </is>
+      </c>
       <c r="O17" s="5" t="inlineStr"/>
-      <c r="P17" s="5" t="inlineStr"/>
-      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
-      <c r="T17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U17" s="5" t="inlineStr"/>
       <c r="V17" s="5" t="inlineStr"/>
       <c r="W17" s="5" t="inlineStr"/>
       <c r="X17" s="5" t="inlineStr"/>
-      <c r="Y17" s="5" t="inlineStr"/>
+      <c r="Y17" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2171,12 +2235,20 @@
       <c r="S20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="T20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>N · Serviços administrativos</t>
+        </is>
+      </c>
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr"/>
-      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2215,16 +2287,40 @@
       </c>
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>61.267.293/0001-62</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ER 2030 FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
       <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Fundos de investimento, exceto previdenciários e imobiliários</t>
+        </is>
+      </c>
       <c r="O21" s="5" t="inlineStr"/>
-      <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
-      <c r="T21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>Fundos de investimento, exceto previdenciários e imobiliários</t>
+        </is>
+      </c>
       <c r="U21" s="5" t="inlineStr"/>
       <c r="V21" s="5" t="inlineStr"/>
       <c r="W21" s="5" t="inlineStr"/>
@@ -2268,13 +2364,33 @@
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>62.144.175/0001-20</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>BANCO PINE S/A</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Bancos múltiplos, com carteira comercial</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R22" s="3" t="n"/>
       <c r="S22" s="3" t="n"/>
       <c r="T22" s="2" t="inlineStr">
@@ -2398,21 +2514,49 @@
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>32.402.502/0001-35</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>QI SOCIEDADE DE CREDITO DIRETO S.A.</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços financeiros não especificadas anteriormente</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R24" s="3" t="n"/>
       <c r="S24" s="3" t="n"/>
-      <c r="T24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr"/>
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr"/>
-      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2589,7 +2733,11 @@
       <c r="S26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="T26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr"/>
       <c r="W26" s="2" t="inlineStr"/>
@@ -2686,7 +2834,11 @@
       <c r="S27" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="T27" s="5" t="inlineStr"/>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>G · Comércio e reparação de veículos</t>
+        </is>
+      </c>
       <c r="U27" s="5" t="inlineStr"/>
       <c r="V27" s="5" t="inlineStr">
         <is>
@@ -2699,7 +2851,11 @@
         </is>
       </c>
       <c r="X27" s="5" t="inlineStr"/>
-      <c r="Y27" s="5" t="inlineStr"/>
+      <c r="Y27" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2787,7 +2943,11 @@
       <c r="S28" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="T28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr"/>
       <c r="W28" s="2" t="inlineStr"/>
@@ -2981,7 +3141,11 @@
       <c r="S30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="2" t="inlineStr"/>
@@ -3095,7 +3259,11 @@
         </is>
       </c>
       <c r="X31" s="5" t="inlineStr"/>
-      <c r="Y31" s="5" t="inlineStr"/>
+      <c r="Y31" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3183,7 +3351,11 @@
       <c r="S32" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="T32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>N · Serviços administrativos</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="2" t="inlineStr"/>
@@ -3385,12 +3557,20 @@
       <c r="S34" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr"/>
       <c r="W34" s="2" t="inlineStr"/>
       <c r="X34" s="2" t="inlineStr"/>
-      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3531,12 +3711,20 @@
       <c r="S36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr"/>
       <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr"/>
-      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3624,12 +3812,20 @@
       <c r="S37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="T37" s="5" t="inlineStr"/>
+      <c r="T37" s="5" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U37" s="5" t="inlineStr"/>
       <c r="V37" s="5" t="inlineStr"/>
       <c r="W37" s="5" t="inlineStr"/>
       <c r="X37" s="5" t="inlineStr"/>
-      <c r="Y37" s="5" t="inlineStr"/>
+      <c r="Y37" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3709,12 +3905,20 @@
       <c r="S38" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>N · Serviços administrativos</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="2" t="inlineStr"/>
       <c r="X38" s="2" t="inlineStr"/>
-      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3766,23 +3970,43 @@
           <t>99.999.999/9999-99</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS MULTISSETORIAL ONE7 LP RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Não classificado</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>Fundos de investimento, exceto previdenciários e imobiliários</t>
+        </is>
+      </c>
       <c r="O39" s="5" t="inlineStr"/>
-      <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="T39" s="5" t="inlineStr"/>
+      <c r="T39" s="5" t="inlineStr">
+        <is>
+          <t>Fundos de investimento, exceto previdenciários e imobiliários</t>
+        </is>
+      </c>
       <c r="U39" s="5" t="inlineStr"/>
       <c r="V39" s="5" t="inlineStr"/>
       <c r="W39" s="5" t="inlineStr"/>
@@ -3888,7 +4112,11 @@
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr"/>
-      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4012,13 +4240,33 @@
           <t>Multicarteira Financeiro</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>48.565.815/0001-44</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>HAPPY CONSIG LTDA</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Atividades de intermediação e agenciamento de serviços e negócios em geral, exceto imobiliários</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr"/>
-      <c r="P42" s="2" t="inlineStr"/>
-      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R42" s="3" t="n"/>
       <c r="S42" s="3" t="n"/>
       <c r="T42" s="2" t="inlineStr">
@@ -4130,12 +4378,20 @@
       <c r="S43" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="T43" s="5" t="inlineStr"/>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U43" s="5" t="inlineStr"/>
       <c r="V43" s="5" t="inlineStr"/>
       <c r="W43" s="5" t="inlineStr"/>
       <c r="X43" s="5" t="inlineStr"/>
-      <c r="Y43" s="5" t="inlineStr"/>
+      <c r="Y43" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4244,7 +4500,11 @@
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr"/>
-      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4353,7 +4613,11 @@
         </is>
       </c>
       <c r="X45" s="5" t="inlineStr"/>
-      <c r="Y45" s="5" t="inlineStr"/>
+      <c r="Y45" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4441,12 +4705,20 @@
       <c r="S46" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="T46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr"/>
       <c r="W46" s="2" t="inlineStr"/>
       <c r="X46" s="2" t="inlineStr"/>
-      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4534,12 +4806,20 @@
       <c r="S47" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="T47" s="5" t="inlineStr"/>
+      <c r="T47" s="5" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U47" s="5" t="inlineStr"/>
       <c r="V47" s="5" t="inlineStr"/>
       <c r="W47" s="5" t="inlineStr"/>
       <c r="X47" s="5" t="inlineStr"/>
-      <c r="Y47" s="5" t="inlineStr"/>
+      <c r="Y47" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4639,13 +4919,33 @@
           <t>Multicarteira Financeiro</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>33.041.260/0652-90</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>GRUPO CASAS BAHIA S.A.</t>
+        </is>
+      </c>
       <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>Comércio varejista especializado de eletrodomésticos e equipamentos de áudio e vídeo</t>
+        </is>
+      </c>
       <c r="O49" s="5" t="inlineStr"/>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
+      <c r="P49" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R49" s="6" t="n"/>
       <c r="S49" s="6" t="n"/>
       <c r="T49" s="5" t="inlineStr">
@@ -4669,7 +4969,11 @@
         </is>
       </c>
       <c r="X49" s="5" t="inlineStr"/>
-      <c r="Y49" s="5" t="inlineStr"/>
+      <c r="Y49" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4839,7 +5143,11 @@
         </is>
       </c>
       <c r="X51" s="5" t="inlineStr"/>
-      <c r="Y51" s="5" t="inlineStr"/>
+      <c r="Y51" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4886,13 +5194,33 @@
           <t>Poder Público</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>62.015.452/0001-02</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>JC CARBON FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Fundos de investimento, exceto previdenciários e imobiliários</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R52" s="3" t="n"/>
       <c r="S52" s="3" t="n"/>
       <c r="T52" s="2" t="inlineStr">
@@ -4955,21 +5283,49 @@
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>54.183.587/0001-40</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>MANSERV MONTAGEM E MANUTENCAO S/A</t>
+        </is>
+      </c>
       <c r="M53" s="5" t="inlineStr"/>
-      <c r="N53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>Instalação e manutenção elétrica</t>
+        </is>
+      </c>
       <c r="O53" s="5" t="inlineStr"/>
-      <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr"/>
+      <c r="P53" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R53" s="6" t="n"/>
       <c r="S53" s="6" t="n"/>
-      <c r="T53" s="5" t="inlineStr"/>
+      <c r="T53" s="5" t="inlineStr">
+        <is>
+          <t>Instalação e manutenção elétrica</t>
+        </is>
+      </c>
       <c r="U53" s="5" t="inlineStr"/>
       <c r="V53" s="5" t="inlineStr"/>
       <c r="W53" s="5" t="inlineStr"/>
       <c r="X53" s="5" t="inlineStr"/>
-      <c r="Y53" s="5" t="inlineStr"/>
+      <c r="Y53" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5016,21 +5372,49 @@
           <t>Crédito Consignado</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>60.939.600/0001-41</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>ARCESP - ASSOCIACAO ASSISTENCIAL</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Atividades associativas não especificadas anteriormente</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R54" s="3" t="n"/>
       <c r="S54" s="3" t="n"/>
-      <c r="T54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>Atividades associativas não especificadas anteriormente</t>
+        </is>
+      </c>
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr"/>
       <c r="W54" s="2" t="inlineStr"/>
       <c r="X54" s="2" t="inlineStr"/>
-      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -5154,21 +5538,49 @@
           <t>Multicarteira Outros</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>01.599.101/0001-93</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>SEQUOIA LOGISTICA E TRANSPORTES S.A</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Transporte rodoviário de carga, exceto produtos perigosos e mudanças, intermunicipal, interestadual e internacional</t>
+        </is>
+      </c>
       <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="inlineStr"/>
-      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R56" s="3" t="n"/>
       <c r="S56" s="3" t="n"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>Transporte rodoviário de carga, exceto produtos perigosos e mudanças, intermunicipal, interestadual e internacional</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr"/>
       <c r="W56" s="2" t="inlineStr"/>
       <c r="X56" s="2" t="inlineStr"/>
-      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -5215,21 +5627,49 @@
           <t>Multicarteira Outros</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr"/>
-      <c r="L57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>29.934.678/0001-23</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>ZIPPI SOLUCOES DE CREDITO LTDA</t>
+        </is>
+      </c>
       <c r="M57" s="5" t="inlineStr"/>
-      <c r="N57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>Correspondentes de instituições financeiras</t>
+        </is>
+      </c>
       <c r="O57" s="5" t="inlineStr"/>
-      <c r="P57" s="5" t="inlineStr"/>
-      <c r="Q57" s="5" t="inlineStr"/>
+      <c r="P57" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R57" s="6" t="n"/>
       <c r="S57" s="6" t="n"/>
-      <c r="T57" s="5" t="inlineStr"/>
+      <c r="T57" s="5" t="inlineStr">
+        <is>
+          <t>Correspondentes de instituições financeiras</t>
+        </is>
+      </c>
       <c r="U57" s="5" t="inlineStr"/>
       <c r="V57" s="5" t="inlineStr"/>
       <c r="W57" s="5" t="inlineStr"/>
       <c r="X57" s="5" t="inlineStr"/>
-      <c r="Y57" s="5" t="inlineStr"/>
+      <c r="Y57" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5329,16 +5769,40 @@
       </c>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
-      <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="inlineStr"/>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>47.242.860/0001-03</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>FS FLORESTAL S.A</t>
+        </is>
+      </c>
       <c r="M59" s="5" t="inlineStr"/>
-      <c r="N59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>Holdings de instituições não-financeiras</t>
+        </is>
+      </c>
       <c r="O59" s="5" t="inlineStr"/>
-      <c r="P59" s="5" t="inlineStr"/>
-      <c r="Q59" s="5" t="inlineStr"/>
+      <c r="P59" s="5" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="Q59" s="5" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R59" s="6" t="n"/>
       <c r="S59" s="6" t="n"/>
-      <c r="T59" s="5" t="inlineStr"/>
+      <c r="T59" s="5" t="inlineStr">
+        <is>
+          <t>Holdings de instituições não-financeiras</t>
+        </is>
+      </c>
       <c r="U59" s="5" t="inlineStr"/>
       <c r="V59" s="5" t="inlineStr"/>
       <c r="W59" s="5" t="inlineStr"/>
@@ -5451,13 +5915,33 @@
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr"/>
-      <c r="K61" s="5" t="inlineStr"/>
-      <c r="L61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>17.479.056/0001-73</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>KOVR PREVIDENCIA S A</t>
+        </is>
+      </c>
       <c r="M61" s="5" t="inlineStr"/>
-      <c r="N61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>Previdência complementar aberta</t>
+        </is>
+      </c>
       <c r="O61" s="5" t="inlineStr"/>
-      <c r="P61" s="5" t="inlineStr"/>
-      <c r="Q61" s="5" t="inlineStr"/>
+      <c r="P61" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q61" s="5" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R61" s="6" t="n"/>
       <c r="S61" s="6" t="n"/>
       <c r="T61" s="5" t="inlineStr">
@@ -5481,7 +5965,11 @@
         </is>
       </c>
       <c r="X61" s="5" t="inlineStr"/>
-      <c r="Y61" s="5" t="inlineStr"/>
+      <c r="Y61" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5569,12 +6057,20 @@
       <c r="S62" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="T62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>C · Indústria de transformação</t>
+        </is>
+      </c>
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr"/>
       <c r="W62" s="2" t="inlineStr"/>
       <c r="X62" s="2" t="inlineStr"/>
-      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5613,21 +6109,49 @@
       </c>
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr"/>
-      <c r="K63" s="5" t="inlineStr"/>
-      <c r="L63" s="5" t="inlineStr"/>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>34.337.707/0001-00</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>BMP SOCIEDADE DE CREDITO DIRETO S.A</t>
+        </is>
+      </c>
       <c r="M63" s="5" t="inlineStr"/>
-      <c r="N63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços financeiros não especificadas anteriormente</t>
+        </is>
+      </c>
       <c r="O63" s="5" t="inlineStr"/>
-      <c r="P63" s="5" t="inlineStr"/>
-      <c r="Q63" s="5" t="inlineStr"/>
+      <c r="P63" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q63" s="5" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R63" s="6" t="n"/>
       <c r="S63" s="6" t="n"/>
-      <c r="T63" s="5" t="inlineStr"/>
+      <c r="T63" s="5" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U63" s="5" t="inlineStr"/>
       <c r="V63" s="5" t="inlineStr"/>
       <c r="W63" s="5" t="inlineStr"/>
       <c r="X63" s="5" t="inlineStr"/>
-      <c r="Y63" s="5" t="inlineStr"/>
+      <c r="Y63" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5796,16 +6320,40 @@
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>64.330.030/0001-49</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE SOL AGORA FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS SEGMENTO FINANCEIRO RESP LIMITADA</t>
+        </is>
+      </c>
       <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Fundos de investimento, exceto previdenciários e imobiliários</t>
+        </is>
+      </c>
       <c r="O66" s="2" t="inlineStr"/>
-      <c r="P66" s="2" t="inlineStr"/>
-      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R66" s="3" t="n"/>
       <c r="S66" s="3" t="n"/>
-      <c r="T66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>Fundos de investimento, exceto previdenciários e imobiliários</t>
+        </is>
+      </c>
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr"/>
       <c r="W66" s="2" t="inlineStr"/>
@@ -5849,21 +6397,49 @@
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr"/>
-      <c r="K67" s="5" t="inlineStr"/>
-      <c r="L67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>52.904.364/0001-08</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>NECTON INVESTIMENTOS S.A. CORRETORA DE VALORES MOBILIARIOS E COMMODITIES</t>
+        </is>
+      </c>
       <c r="M67" s="5" t="inlineStr"/>
-      <c r="N67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>Corretoras de títulos e valores mobiliários</t>
+        </is>
+      </c>
       <c r="O67" s="5" t="inlineStr"/>
-      <c r="P67" s="5" t="inlineStr"/>
-      <c r="Q67" s="5" t="inlineStr"/>
+      <c r="P67" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R67" s="6" t="n"/>
       <c r="S67" s="6" t="n"/>
-      <c r="T67" s="5" t="inlineStr"/>
+      <c r="T67" s="5" t="inlineStr">
+        <is>
+          <t>Corretoras de títulos e valores mobiliários</t>
+        </is>
+      </c>
       <c r="U67" s="5" t="inlineStr"/>
       <c r="V67" s="5" t="inlineStr"/>
       <c r="W67" s="5" t="inlineStr"/>
       <c r="X67" s="5" t="inlineStr"/>
-      <c r="Y67" s="5" t="inlineStr"/>
+      <c r="Y67" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5910,16 +6486,40 @@
           <t>Crédito Pessoal</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>29.720.593/0001-42</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS ANGA MULTI CONSIGNADOS I RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
       <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Fundos de investimento, exceto previdenciários e imobiliários</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="inlineStr"/>
-      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R68" s="3" t="n"/>
       <c r="S68" s="3" t="n"/>
-      <c r="T68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr"/>
       <c r="W68" s="2" t="inlineStr"/>
@@ -6016,13 +6616,33 @@
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>48.632.754/0001-90</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>CELCOIN SOCIEDADE DE CREDITO DIRETO S.A</t>
+        </is>
+      </c>
       <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Outras instituições de intermediação não-monetária não especificadas anteriormente</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R70" s="3" t="n"/>
       <c r="S70" s="3" t="n"/>
       <c r="T70" s="2" t="inlineStr">
@@ -6046,7 +6666,11 @@
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr"/>
-      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6093,21 +6717,49 @@
           <t>Multicarteira Outros</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr"/>
-      <c r="L71" s="5" t="inlineStr"/>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>10.989.834/0001-25</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>BMG FOODS IMPORTACAO E EXPORTACAO LTDA</t>
+        </is>
+      </c>
       <c r="M71" s="5" t="inlineStr"/>
-      <c r="N71" s="5" t="inlineStr"/>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>Comércio atacadista de carnes bovinas e suínas e derivados</t>
+        </is>
+      </c>
       <c r="O71" s="5" t="inlineStr"/>
-      <c r="P71" s="5" t="inlineStr"/>
-      <c r="Q71" s="5" t="inlineStr"/>
+      <c r="P71" s="5" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="Q71" s="5" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R71" s="6" t="n"/>
       <c r="S71" s="6" t="n"/>
-      <c r="T71" s="5" t="inlineStr"/>
+      <c r="T71" s="5" t="inlineStr">
+        <is>
+          <t>G · Comércio e reparação de veículos</t>
+        </is>
+      </c>
       <c r="U71" s="5" t="inlineStr"/>
       <c r="V71" s="5" t="inlineStr"/>
       <c r="W71" s="5" t="inlineStr"/>
       <c r="X71" s="5" t="inlineStr"/>
-      <c r="Y71" s="5" t="inlineStr"/>
+      <c r="Y71" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -6146,21 +6798,49 @@
       </c>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>32.402.502/0001-35</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>QI SOCIEDADE DE CREDITO DIRETO S.A.</t>
+        </is>
+      </c>
       <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços financeiros não especificadas anteriormente</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="inlineStr"/>
-      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R72" s="3" t="n"/>
       <c r="S72" s="3" t="n"/>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr"/>
       <c r="W72" s="2" t="inlineStr"/>
       <c r="X72" s="2" t="inlineStr"/>
-      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6207,13 +6887,33 @@
           <t>Crédito Consignado</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr"/>
-      <c r="L73" s="5" t="inlineStr"/>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>32.402.502/0001-35</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>QI SOCIEDADE DE CREDITO DIRETO S.A.</t>
+        </is>
+      </c>
       <c r="M73" s="5" t="inlineStr"/>
-      <c r="N73" s="5" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços financeiros não especificadas anteriormente</t>
+        </is>
+      </c>
       <c r="O73" s="5" t="inlineStr"/>
-      <c r="P73" s="5" t="inlineStr"/>
-      <c r="Q73" s="5" t="inlineStr"/>
+      <c r="P73" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q73" s="5" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R73" s="6" t="n"/>
       <c r="S73" s="6" t="n"/>
       <c r="T73" s="5" t="inlineStr">
@@ -6237,7 +6937,11 @@
         </is>
       </c>
       <c r="X73" s="5" t="inlineStr"/>
-      <c r="Y73" s="5" t="inlineStr"/>
+      <c r="Y73" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -6276,16 +6980,40 @@
       </c>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>62.144.175/0001-20</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>BANCO PINE S/A</t>
+        </is>
+      </c>
       <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Bancos múltiplos, com carteira comercial</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R74" s="3" t="n"/>
       <c r="S74" s="3" t="n"/>
-      <c r="T74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>Bancos múltiplos, com carteira comercial</t>
+        </is>
+      </c>
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr"/>
       <c r="W74" s="2" t="inlineStr"/>
@@ -6329,21 +7057,49 @@
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="5" t="inlineStr"/>
-      <c r="K75" s="5" t="inlineStr"/>
-      <c r="L75" s="5" t="inlineStr"/>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>36.947.229/0001-85</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>COBUCCIO S/A SOCIEDADE DE CREDITO, FINANCIAMENTO E INVESTIMENTOS</t>
+        </is>
+      </c>
       <c r="M75" s="5" t="inlineStr"/>
-      <c r="N75" s="5" t="inlineStr"/>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>Sociedades de crédito, financiamento e investimento - financeiras</t>
+        </is>
+      </c>
       <c r="O75" s="5" t="inlineStr"/>
-      <c r="P75" s="5" t="inlineStr"/>
-      <c r="Q75" s="5" t="inlineStr"/>
+      <c r="P75" s="5" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="Q75" s="5" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R75" s="6" t="n"/>
       <c r="S75" s="6" t="n"/>
-      <c r="T75" s="5" t="inlineStr"/>
+      <c r="T75" s="5" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U75" s="5" t="inlineStr"/>
       <c r="V75" s="5" t="inlineStr"/>
       <c r="W75" s="5" t="inlineStr"/>
       <c r="X75" s="5" t="inlineStr"/>
-      <c r="Y75" s="5" t="inlineStr"/>
+      <c r="Y75" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -6443,13 +7199,33 @@
           <t>Crédito Consignado</t>
         </is>
       </c>
-      <c r="K77" s="5" t="inlineStr"/>
-      <c r="L77" s="5" t="inlineStr"/>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>32.402.502/0001-35</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>QI SOCIEDADE DE CREDITO DIRETO S.A.</t>
+        </is>
+      </c>
       <c r="M77" s="5" t="inlineStr"/>
-      <c r="N77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços financeiros não especificadas anteriormente</t>
+        </is>
+      </c>
       <c r="O77" s="5" t="inlineStr"/>
-      <c r="P77" s="5" t="inlineStr"/>
-      <c r="Q77" s="5" t="inlineStr"/>
+      <c r="P77" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q77" s="5" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R77" s="6" t="n"/>
       <c r="S77" s="6" t="n"/>
       <c r="T77" s="5" t="inlineStr">
@@ -6473,7 +7249,11 @@
         </is>
       </c>
       <c r="X77" s="5" t="inlineStr"/>
-      <c r="Y77" s="5" t="inlineStr"/>
+      <c r="Y77" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -6512,21 +7292,49 @@
       </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>02.773.542/0001-22</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>OPEA SECURITIZADORA S.A.</t>
+        </is>
+      </c>
       <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Securitização de créditos</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="inlineStr"/>
-      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R78" s="3" t="n"/>
       <c r="S78" s="3" t="n"/>
-      <c r="T78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr"/>
       <c r="W78" s="2" t="inlineStr"/>
       <c r="X78" s="2" t="inlineStr"/>
-      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -6565,13 +7373,33 @@
       </c>
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="5" t="inlineStr"/>
-      <c r="K79" s="5" t="inlineStr"/>
-      <c r="L79" s="5" t="inlineStr"/>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>09.358.882/0001-36</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA VISTA ALEGRE LTDA</t>
+        </is>
+      </c>
       <c r="M79" s="5" t="inlineStr"/>
-      <c r="N79" s="5" t="inlineStr"/>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>Criação de bovinos para corte</t>
+        </is>
+      </c>
       <c r="O79" s="5" t="inlineStr"/>
-      <c r="P79" s="5" t="inlineStr"/>
-      <c r="Q79" s="5" t="inlineStr"/>
+      <c r="P79" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q79" s="5" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R79" s="6" t="n"/>
       <c r="S79" s="6" t="n"/>
       <c r="T79" s="5" t="inlineStr">
@@ -6587,7 +7415,11 @@
       <c r="V79" s="5" t="inlineStr"/>
       <c r="W79" s="5" t="inlineStr"/>
       <c r="X79" s="5" t="inlineStr"/>
-      <c r="Y79" s="5" t="inlineStr"/>
+      <c r="Y79" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -6634,13 +7466,33 @@
           <t>Fomento Mercantil</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>25.043.891/0001-94</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS XPCE III</t>
+        </is>
+      </c>
       <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Fundos de investimento, exceto previdenciários e imobiliários</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="inlineStr"/>
-      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R80" s="3" t="n"/>
       <c r="S80" s="3" t="n"/>
       <c r="T80" s="2" t="inlineStr">
@@ -6711,21 +7563,49 @@
           <t>Crédito Pessoal</t>
         </is>
       </c>
-      <c r="K81" s="5" t="inlineStr"/>
-      <c r="L81" s="5" t="inlineStr"/>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>39.587.424/0001-30</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>UY3 SOCIEDADE DE CREDITO DIRETO S/A</t>
+        </is>
+      </c>
       <c r="M81" s="5" t="inlineStr"/>
-      <c r="N81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>Outras atividades auxiliares dos serviços financeiros não especificadas anteriormente</t>
+        </is>
+      </c>
       <c r="O81" s="5" t="inlineStr"/>
-      <c r="P81" s="5" t="inlineStr"/>
-      <c r="Q81" s="5" t="inlineStr"/>
+      <c r="P81" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="Q81" s="5" t="inlineStr">
+        <is>
+          <t>Demais</t>
+        </is>
+      </c>
       <c r="R81" s="6" t="n"/>
       <c r="S81" s="6" t="n"/>
-      <c r="T81" s="5" t="inlineStr"/>
+      <c r="T81" s="5" t="inlineStr">
+        <is>
+          <t>K · Atividades financeiras e seguros</t>
+        </is>
+      </c>
       <c r="U81" s="5" t="inlineStr"/>
       <c r="V81" s="5" t="inlineStr"/>
       <c r="W81" s="5" t="inlineStr"/>
       <c r="X81" s="5" t="inlineStr"/>
-      <c r="Y81" s="5" t="inlineStr"/>
+      <c r="Y81" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6849,21 +7729,49 @@
           <t>Fomento Mercantil</t>
         </is>
       </c>
-      <c r="K83" s="5" t="inlineStr"/>
-      <c r="L83" s="5" t="inlineStr"/>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>64.643.657/0001-50</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>NEXUS ORGANIZACOES E NEGOCIOS LTDA</t>
+        </is>
+      </c>
       <c r="M83" s="5" t="inlineStr"/>
-      <c r="N83" s="5" t="inlineStr"/>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>Incorporação de empreendimentos imobiliários</t>
+        </is>
+      </c>
       <c r="O83" s="5" t="inlineStr"/>
-      <c r="P83" s="5" t="inlineStr"/>
-      <c r="Q83" s="5" t="inlineStr"/>
+      <c r="P83" s="5" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="Q83" s="5" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R83" s="6" t="n"/>
       <c r="S83" s="6" t="n"/>
-      <c r="T83" s="5" t="inlineStr"/>
+      <c r="T83" s="5" t="inlineStr">
+        <is>
+          <t>Incorporação de empreendimentos imobiliários</t>
+        </is>
+      </c>
       <c r="U83" s="5" t="inlineStr"/>
       <c r="V83" s="5" t="inlineStr"/>
       <c r="W83" s="5" t="inlineStr"/>
       <c r="X83" s="5" t="inlineStr"/>
-      <c r="Y83" s="5" t="inlineStr"/>
+      <c r="Y83" s="5" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6902,13 +7810,33 @@
       </c>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>39.268.207/0001-87</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>CAIQUE CASTRO SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+        </is>
+      </c>
       <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Serviços advocatícios</t>
+        </is>
+      </c>
       <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="inlineStr"/>
-      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>EMPRESA DE PEQUENO PORTE</t>
+        </is>
+      </c>
       <c r="R84" s="3" t="n"/>
       <c r="S84" s="3" t="n"/>
       <c r="T84" s="2" t="inlineStr">
@@ -6971,13 +7899,33 @@
       </c>
       <c r="I85" s="5" t="inlineStr"/>
       <c r="J85" s="5" t="inlineStr"/>
-      <c r="K85" s="5" t="inlineStr"/>
-      <c r="L85" s="5" t="inlineStr"/>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>63.679.105/0001-39</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>FUNDO DE INVESTIMENTO EM COTAS DE FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS RIZA SRM - RESPONSAB</t>
+        </is>
+      </c>
       <c r="M85" s="5" t="inlineStr"/>
-      <c r="N85" s="5" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>Fundos de investimento, exceto previdenciários e imobiliários</t>
+        </is>
+      </c>
       <c r="O85" s="5" t="inlineStr"/>
-      <c r="P85" s="5" t="inlineStr"/>
-      <c r="Q85" s="5" t="inlineStr"/>
+      <c r="P85" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q85" s="5" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R85" s="6" t="n"/>
       <c r="S85" s="6" t="n"/>
       <c r="T85" s="5" t="inlineStr">
@@ -7048,21 +7996,49 @@
           <t>Agronegócio</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>61.150.348/0001-50</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>COMPANHIA NITRO QUIMICA BRASILEIRA</t>
+        </is>
+      </c>
       <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Fabricação de outros produtos químicos inorgânicos não especificados anteriormente</t>
+        </is>
+      </c>
       <c r="O86" s="2" t="inlineStr"/>
-      <c r="P86" s="2" t="inlineStr"/>
-      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R86" s="3" t="n"/>
       <c r="S86" s="3" t="n"/>
-      <c r="T86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>Fabricação de outros produtos químicos inorgânicos não especificados anteriormente</t>
+        </is>
+      </c>
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr"/>
       <c r="W86" s="2" t="inlineStr"/>
       <c r="X86" s="2" t="inlineStr"/>
-      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -7162,21 +8138,49 @@
       </c>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>61.150.348/0001-50</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>COMPANHIA NITRO QUIMICA BRASILEIRA</t>
+        </is>
+      </c>
       <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Fabricação de outros produtos químicos inorgânicos não especificados anteriormente</t>
+        </is>
+      </c>
       <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="inlineStr"/>
-      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>DEMAIS</t>
+        </is>
+      </c>
       <c r="R88" s="3" t="n"/>
       <c r="S88" s="3" t="n"/>
-      <c r="T88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>Fabricação de outros produtos químicos inorgânicos não especificados anteriormente</t>
+        </is>
+      </c>
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr"/>
       <c r="W88" s="2" t="inlineStr"/>
       <c r="X88" s="2" t="inlineStr"/>
-      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>Provável</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -7337,7 +8341,11 @@
       </c>
       <c r="I91" s="5" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr"/>
-      <c r="K91" s="5" t="inlineStr"/>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>00.093.526/3692-91</t>
+        </is>
+      </c>
       <c r="L91" s="5" t="inlineStr"/>
       <c r="M91" s="5" t="inlineStr"/>
       <c r="N91" s="5" t="inlineStr"/>
